--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3743,6 +3743,133 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114673367</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57381</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hälsingbo (Hälsingbo), Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>565364</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6701932</v>
+      </c>
+      <c r="S28" t="n">
+        <v>15</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-02-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -3875,7 +3875,7 @@
         <v>118760246</v>
       </c>
       <c r="B29" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -3988,7 +3988,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119750678</v>
+        <v>119750677</v>
       </c>
       <c r="B30" t="n">
         <v>97907</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4031,16 +4031,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565385</v>
+        <v>565433</v>
       </c>
       <c r="R30" t="n">
-        <v>6702024</v>
+        <v>6701957</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4075,12 +4082,18 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4099,10 +4112,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119750672</v>
+        <v>119750676</v>
       </c>
       <c r="B31" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4111,38 +4124,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565468</v>
+        <v>565477</v>
       </c>
       <c r="R31" t="n">
-        <v>6701956</v>
+        <v>6701995</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4177,12 +4197,18 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4201,7 +4227,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119750676</v>
+        <v>119750678</v>
       </c>
       <c r="B32" t="n">
         <v>97907</v>
@@ -4234,24 +4260,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565477</v>
+        <v>565385</v>
       </c>
       <c r="R32" t="n">
-        <v>6701995</v>
+        <v>6702024</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4286,18 +4314,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4316,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119750677</v>
+        <v>119750672</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4328,54 +4350,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565433</v>
+        <v>565468</v>
       </c>
       <c r="R33" t="n">
-        <v>6701957</v>
+        <v>6701956</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4410,18 +4416,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -3988,10 +3988,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119750677</v>
+        <v>119750672</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4000,54 +4000,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565433</v>
+        <v>565468</v>
       </c>
       <c r="R30" t="n">
-        <v>6701957</v>
+        <v>6701956</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4082,18 +4066,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4112,7 +4090,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119750676</v>
+        <v>119750677</v>
       </c>
       <c r="B31" t="n">
         <v>97907</v>
@@ -4145,7 +4123,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -4159,10 +4146,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565477</v>
+        <v>565433</v>
       </c>
       <c r="R31" t="n">
-        <v>6701995</v>
+        <v>6701957</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4338,10 +4325,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119750672</v>
+        <v>119750676</v>
       </c>
       <c r="B33" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4350,38 +4337,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565468</v>
+        <v>565477</v>
       </c>
       <c r="R33" t="n">
-        <v>6701956</v>
+        <v>6701995</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,12 +4410,18 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -3988,10 +3988,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119750672</v>
+        <v>119750676</v>
       </c>
       <c r="B30" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4000,38 +4000,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565468</v>
+        <v>565477</v>
       </c>
       <c r="R30" t="n">
-        <v>6701956</v>
+        <v>6701995</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4066,12 +4073,18 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4325,10 +4338,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119750676</v>
+        <v>119750672</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4337,45 +4350,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565477</v>
+        <v>565468</v>
       </c>
       <c r="R33" t="n">
-        <v>6701995</v>
+        <v>6701956</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4410,18 +4416,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -3988,10 +3988,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119750676</v>
+        <v>119750677</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4021,7 +4021,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -4035,10 +4044,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>565477</v>
+        <v>565433</v>
       </c>
       <c r="R30" t="n">
-        <v>6701995</v>
+        <v>6701957</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4103,10 +4112,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119750677</v>
+        <v>119750678</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4138,7 +4147,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4146,23 +4155,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>565433</v>
+        <v>565385</v>
       </c>
       <c r="R31" t="n">
-        <v>6701957</v>
+        <v>6702024</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4197,18 +4199,12 @@
           <t>2024-09-14</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1 blomstjälk</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4227,10 +4223,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119750678</v>
+        <v>119750672</v>
       </c>
       <c r="B32" t="n">
-        <v>97907</v>
+        <v>90545</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4239,47 +4235,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>565385</v>
+        <v>565468</v>
       </c>
       <c r="R32" t="n">
-        <v>6702024</v>
+        <v>6701956</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4338,10 +4325,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119750672</v>
+        <v>119750676</v>
       </c>
       <c r="B33" t="n">
-        <v>90527</v>
+        <v>97930</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4350,38 +4337,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hälsingbo, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>565468</v>
+        <v>565477</v>
       </c>
       <c r="R33" t="n">
-        <v>6701956</v>
+        <v>6701995</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,12 +4410,18 @@
           <t>2024-09-14</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1 blomstjälk</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4438,6 +4438,210 @@
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121694258</v>
+      </c>
+      <c r="B34" t="n">
+        <v>90941</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1618</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Hängticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Postia ceriflua</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>565411</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6701952</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121694257</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90728</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>565411</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6701953</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4440,10 +4440,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121694257</v>
+        <v>121694258</v>
       </c>
       <c r="B34" t="n">
-        <v>90728</v>
+        <v>90941</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4452,25 +4452,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1618</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4483,7 +4483,7 @@
         <v>565411</v>
       </c>
       <c r="R34" t="n">
-        <v>6701953</v>
+        <v>6701952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121694258</v>
+        <v>121694257</v>
       </c>
       <c r="B35" t="n">
-        <v>90941</v>
+        <v>90728</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4554,25 +4554,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1618</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
         <v>565411</v>
       </c>
       <c r="R35" t="n">
-        <v>6701952</v>
+        <v>6701953</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4440,10 +4440,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121694258</v>
+        <v>121694257</v>
       </c>
       <c r="B34" t="n">
-        <v>90941</v>
+        <v>90728</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4452,25 +4452,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1618</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4483,7 +4483,7 @@
         <v>565411</v>
       </c>
       <c r="R34" t="n">
-        <v>6701952</v>
+        <v>6701953</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121694257</v>
+        <v>121694258</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>90941</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4554,25 +4554,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1618</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
         <v>565411</v>
       </c>
       <c r="R35" t="n">
-        <v>6701953</v>
+        <v>6701952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4443,7 +4443,7 @@
         <v>121694257</v>
       </c>
       <c r="B34" t="n">
-        <v>90728</v>
+        <v>90742</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>121694258</v>
       </c>
       <c r="B35" t="n">
-        <v>90941</v>
+        <v>90955</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4440,10 +4440,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121694257</v>
+        <v>121694258</v>
       </c>
       <c r="B34" t="n">
-        <v>90742</v>
+        <v>90957</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4452,25 +4452,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>1618</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4483,7 +4483,7 @@
         <v>565411</v>
       </c>
       <c r="R34" t="n">
-        <v>6701953</v>
+        <v>6701952</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121694258</v>
+        <v>121694257</v>
       </c>
       <c r="B35" t="n">
-        <v>90955</v>
+        <v>90744</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4554,25 +4554,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1618</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
         <v>565411</v>
       </c>
       <c r="R35" t="n">
-        <v>6701952</v>
+        <v>6701953</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4443,7 +4443,7 @@
         <v>121694258</v>
       </c>
       <c r="B34" t="n">
-        <v>90957</v>
+        <v>90958</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>121694257</v>
       </c>
       <c r="B35" t="n">
-        <v>90744</v>
+        <v>90745</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4440,10 +4440,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121694258</v>
+        <v>121694257</v>
       </c>
       <c r="B34" t="n">
-        <v>90958</v>
+        <v>90754</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4452,25 +4452,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1618</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hängticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Postia ceriflua</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4483,7 +4483,7 @@
         <v>565411</v>
       </c>
       <c r="R34" t="n">
-        <v>6701952</v>
+        <v>6701953</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4542,10 +4542,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121694257</v>
+        <v>121694258</v>
       </c>
       <c r="B35" t="n">
-        <v>90745</v>
+        <v>90967</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4554,25 +4554,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1618</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hängticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Postia ceriflua</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Jülich</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4585,7 +4585,7 @@
         <v>565411</v>
       </c>
       <c r="R35" t="n">
-        <v>6701953</v>
+        <v>6701952</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4642,6 +4642,113 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123977693</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>565474</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6701989</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>127056021</v>
       </c>
       <c r="B37" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127056028</v>
       </c>
       <c r="B38" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>127056037</v>
       </c>
       <c r="B39" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>127056025</v>
       </c>
       <c r="B40" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>127056023</v>
       </c>
       <c r="B41" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126998946</v>
       </c>
       <c r="B42" t="n">
-        <v>92569</v>
+        <v>92643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>127056021</v>
       </c>
       <c r="B37" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127056028</v>
       </c>
       <c r="B38" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>127056037</v>
       </c>
       <c r="B39" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>127056025</v>
       </c>
       <c r="B40" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>127056023</v>
       </c>
       <c r="B41" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126998946</v>
       </c>
       <c r="B42" t="n">
-        <v>92643</v>
+        <v>92649</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>127056021</v>
       </c>
       <c r="B37" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127056028</v>
       </c>
       <c r="B38" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>127056037</v>
       </c>
       <c r="B39" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>127056025</v>
       </c>
       <c r="B40" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>127056023</v>
       </c>
       <c r="B41" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126998946</v>
       </c>
       <c r="B42" t="n">
-        <v>92649</v>
+        <v>92650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>127056021</v>
       </c>
       <c r="B37" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127056028</v>
       </c>
       <c r="B38" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>127056037</v>
       </c>
       <c r="B39" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>127056025</v>
       </c>
       <c r="B40" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>127056023</v>
       </c>
       <c r="B41" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126998946</v>
       </c>
       <c r="B42" t="n">
-        <v>92650</v>
+        <v>92654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>127056021</v>
       </c>
       <c r="B37" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127056028</v>
       </c>
       <c r="B38" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>127056037</v>
       </c>
       <c r="B39" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>127056025</v>
       </c>
       <c r="B40" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>127056023</v>
       </c>
       <c r="B41" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>127056021</v>
       </c>
       <c r="B37" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127056028</v>
       </c>
       <c r="B38" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>127056037</v>
       </c>
       <c r="B39" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>127056025</v>
       </c>
       <c r="B40" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>127056023</v>
       </c>
       <c r="B41" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126998946</v>
       </c>
       <c r="B42" t="n">
-        <v>92654</v>
+        <v>92656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5416,6 +5416,205 @@
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127821561</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91332</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>565429</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6701966</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127821563</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>565401</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6701989</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>127056021</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127056028</v>
       </c>
       <c r="B38" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>127056037</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>127056025</v>
       </c>
       <c r="B40" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>127056023</v>
       </c>
       <c r="B41" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126998946</v>
       </c>
       <c r="B42" t="n">
-        <v>92656</v>
+        <v>92662</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>127821561</v>
       </c>
       <c r="B43" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5314,7 +5314,7 @@
         <v>126998946</v>
       </c>
       <c r="B42" t="n">
-        <v>92662</v>
+        <v>92665</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>127821561</v>
       </c>
       <c r="B43" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>127821563</v>
       </c>
       <c r="B44" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5421,7 +5421,7 @@
         <v>127821561</v>
       </c>
       <c r="B43" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>127821563</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5421,7 +5421,7 @@
         <v>127821561</v>
       </c>
       <c r="B43" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5421,7 +5421,7 @@
         <v>127821561</v>
       </c>
       <c r="B43" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5421,7 +5421,7 @@
         <v>127821561</v>
       </c>
       <c r="B43" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5421,7 +5421,7 @@
         <v>127821561</v>
       </c>
       <c r="B43" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>127821563</v>
       </c>
       <c r="B44" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5421,7 +5421,7 @@
         <v>127821561</v>
       </c>
       <c r="B43" t="n">
-        <v>91360</v>
+        <v>91452</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>127821563</v>
       </c>
       <c r="B44" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5615,6 +5615,220 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130008052</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>565445</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6702000</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130008066</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92024</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>565434</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6702000</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-06</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5620,7 +5620,7 @@
         <v>130008052</v>
       </c>
       <c r="B45" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>130008066</v>
       </c>
       <c r="B46" t="n">
-        <v>92024</v>
+        <v>92025</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5617,10 +5617,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130008052</v>
+        <v>130008066</v>
       </c>
       <c r="B45" t="n">
-        <v>91606</v>
+        <v>92042</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5628,21 +5628,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>565445</v>
+        <v>565434</v>
       </c>
       <c r="R45" t="n">
         <v>6702000</v>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,10 +5724,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130008066</v>
+        <v>130008052</v>
       </c>
       <c r="B46" t="n">
-        <v>92025</v>
+        <v>91623</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565434</v>
+        <v>565445</v>
       </c>
       <c r="R46" t="n">
         <v>6702000</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5620,7 +5620,7 @@
         <v>130008066</v>
       </c>
       <c r="B45" t="n">
-        <v>92058</v>
+        <v>92060</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>130008052</v>
       </c>
       <c r="B46" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5828,6 +5828,220 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130243319</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92012</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>565376</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6702009</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130243318</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hälsingbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>565372</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6702009</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -4754,7 +4754,7 @@
         <v>127056021</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>127056028</v>
       </c>
       <c r="B38" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4981,7 +4981,7 @@
         <v>127056037</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>127056025</v>
       </c>
       <c r="B40" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>127056023</v>
       </c>
       <c r="B41" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>126998946</v>
       </c>
       <c r="B42" t="n">
-        <v>92665</v>
+        <v>92643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5617,10 +5617,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130008066</v>
+        <v>130008052</v>
       </c>
       <c r="B45" t="n">
-        <v>92060</v>
+        <v>91728</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5628,21 +5628,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6040186</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5652,7 +5652,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>565434</v>
+        <v>565445</v>
       </c>
       <c r="R45" t="n">
         <v>6702000</v>
@@ -5687,7 +5687,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5724,10 +5724,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130008052</v>
+        <v>130008066</v>
       </c>
       <c r="B46" t="n">
-        <v>91641</v>
+        <v>92147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5735,21 +5735,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6040186</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kötticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>565445</v>
+        <v>565434</v>
       </c>
       <c r="R46" t="n">
         <v>6702000</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5834,7 +5834,7 @@
         <v>130243319</v>
       </c>
       <c r="B47" t="n">
-        <v>92012</v>
+        <v>92099</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>130243318</v>
       </c>
       <c r="B48" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5834,7 +5834,7 @@
         <v>130243319</v>
       </c>
       <c r="B47" t="n">
-        <v>92099</v>
+        <v>92102</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>130243318</v>
       </c>
       <c r="B48" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5834,7 +5834,7 @@
         <v>130243319</v>
       </c>
       <c r="B47" t="n">
-        <v>92102</v>
+        <v>92128</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>130243318</v>
       </c>
       <c r="B48" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5834,7 +5834,7 @@
         <v>130243319</v>
       </c>
       <c r="B47" t="n">
-        <v>92128</v>
+        <v>92129</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>130243318</v>
       </c>
       <c r="B48" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5834,7 +5834,7 @@
         <v>130243319</v>
       </c>
       <c r="B47" t="n">
-        <v>92129</v>
+        <v>92130</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>130243318</v>
       </c>
       <c r="B48" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 58505-2022 artfynd.xlsx
+++ b/artfynd/A 58505-2022 artfynd.xlsx
@@ -5834,7 +5834,7 @@
         <v>130243319</v>
       </c>
       <c r="B47" t="n">
-        <v>92130</v>
+        <v>92132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>130243318</v>
       </c>
       <c r="B48" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
